--- a/output/summary_tables/Financial Assurance Module Summary Tables.xlsx
+++ b/output/summary_tables/Financial Assurance Module Summary Tables.xlsx
@@ -463,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Financial Assurance - cost estimates for closure, post-closure, and cleanup that facilities must be able to pay for; held mainly by permitted TSDF.</t>
+          <t>Financial Assurance - cost estimates for closure, post-closure, and cleanup that facilities must be able to pay for; held mainly by permitted TSDF. Summarized from the FA_MASTER master file.</t>
         </is>
       </c>
       <c r="B1" s="7"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Identifier: HANDLER_ID, one row per cost-estimate coverage.</t>
+          <t>Identifier: HANDLER_ID, one row per cost estimate x mechanism detail combination.</t>
         </is>
       </c>
       <c r="B2" s="7"/>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <v>22448</v>
+        <v>29863</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2 other columns not summarized (identifiers, names, and descriptions / free-text fields).</t>
+          <t>6 other columns are not summarized because they hold record identifiers, personal names and staff identifiers, correspondence addresses and contact details, free-text notes, or the description text paired with a code that is summarized here. They are named below the table.</t>
         </is>
       </c>
       <c r="C5" s="7"/>
@@ -584,6 +584,129 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">COST_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the cost estimate.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C7" s="11">
+        <v>54</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E7" s="12">
+        <v>7.7</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E8" s="12">
+        <v>7.1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E9" s="12">
+        <v>6.8</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E10" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E11" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>All Other (49)</t>
+        </is>
+      </c>
+      <c r="E12" s="12">
+        <v>66.9</v>
+      </c>
+      <c r="F12" s="10">
+        <v>19976</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -604,109 +727,109 @@
           </r>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>0%
 (0)</t>
         </is>
       </c>
-      <c r="C7" s="11">
+      <c r="C13" s="11">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>C - Closure</t>
         </is>
       </c>
-      <c r="E7" s="12">
-        <v>32.5</v>
-      </c>
-      <c r="F7" s="10">
-        <v>7301</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="E13" s="12">
+        <v>33.3</v>
+      </c>
+      <c r="F13" s="10">
+        <v>9944</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>P - Post-Closure Care</t>
         </is>
       </c>
-      <c r="E8" s="12">
-        <v>26</v>
-      </c>
-      <c r="F8" s="10">
-        <v>5846</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="E14" s="12">
+        <v>27.3</v>
+      </c>
+      <c r="F14" s="10">
+        <v>8159</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>A - Corrective Action</t>
         </is>
       </c>
-      <c r="E9" s="12">
-        <v>22.2</v>
-      </c>
-      <c r="F9" s="10">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="E15" s="12">
+        <v>24.1</v>
+      </c>
+      <c r="F15" s="10">
+        <v>7189</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>S - Sudden Third-Party Liability</t>
         </is>
       </c>
-      <c r="E10" s="12">
-        <v>10.2</v>
-      </c>
-      <c r="F10" s="10">
-        <v>2293</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="E16" s="12">
+        <v>8.1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>B - Sudden And Non-Sudden Third-Party Liability</t>
         </is>
       </c>
-      <c r="E11" s="12">
-        <v>7.9</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="E17" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>N - Non-Sudden Third-Party Liability</t>
         </is>
       </c>
-      <c r="E12" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="F12" s="10">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="E18" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -727,45 +850,45 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>0%
 (0)</t>
         </is>
       </c>
-      <c r="C13" s="11">
+      <c r="C19" s="11">
         <v>2</v>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>S - State</t>
         </is>
       </c>
-      <c r="E13" s="12">
-        <v>92.6</v>
-      </c>
-      <c r="F13" s="10">
-        <v>20798</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="E19" s="12">
+        <v>92.1</v>
+      </c>
+      <c r="F19" s="10">
+        <v>27512</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>E - EPA</t>
         </is>
       </c>
-      <c r="E14" s="12">
-        <v>7.4</v>
-      </c>
-      <c r="F14" s="10">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="E20" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="F20" s="10">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -773,7 +896,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">COST_ACTIVITY_LOCATION
+            <t xml:space="preserve">COST_ESTIMATE_REASON
 </t>
           </r>
           <r>
@@ -782,113 +905,113 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>State or territory whose implementing agency is responsible for the cost estimate.</t>
+            <t>Reason the cost estimate was submitted or updated.</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C15" s="11">
-        <v>54</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="E15" s="12">
-        <v>9.1</v>
-      </c>
-      <c r="F15" s="10">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="E16" s="12">
-        <v>6.9</v>
-      </c>
-      <c r="F16" s="10">
-        <v>1556</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="E17" s="12">
-        <v>6.2</v>
-      </c>
-      <c r="F17" s="10">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E18" s="12">
-        <v>5.9</v>
-      </c>
-      <c r="F18" s="10">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="E19" s="12">
-        <v>4.6</v>
-      </c>
-      <c r="F19" s="10">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>All Other (49)</t>
-        </is>
-      </c>
-      <c r="E20" s="12">
-        <v>67.2</v>
-      </c>
-      <c r="F20" s="10">
-        <v>15091</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>0.5%
+(138)</t>
+        </is>
+      </c>
+      <c r="C21" s="11">
+        <v>13</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>A - Inflation Adjusted</t>
+        </is>
+      </c>
+      <c r="E21" s="12">
+        <v>51.9</v>
+      </c>
+      <c r="F21" s="10">
+        <v>15494</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>R - Revised Cost Estimate (Modifications And R...</t>
+        </is>
+      </c>
+      <c r="E22" s="12">
+        <v>23</v>
+      </c>
+      <c r="F22" s="10">
+        <v>6862</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>L - Liability Coverage Required</t>
+        </is>
+      </c>
+      <c r="E23" s="12">
+        <v>10.5</v>
+      </c>
+      <c r="F23" s="10">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>I - Initial Cost Estimate</t>
+        </is>
+      </c>
+      <c r="E24" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="F24" s="10">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>C - Cost Estimate Not Required Or No Longer Re...</t>
+        </is>
+      </c>
+      <c r="E25" s="12">
+        <v>4</v>
+      </c>
+      <c r="F25" s="10">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>All Other (8)</t>
+        </is>
+      </c>
+      <c r="E26" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="F26" s="10">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -909,109 +1032,109 @@
           </r>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>22.1%
-(4966)</t>
-        </is>
-      </c>
-      <c r="C21" s="11">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>19.7%
+(5874)</t>
+        </is>
+      </c>
+      <c r="C27" s="11">
         <v>55</v>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E27" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F27" s="10">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E28" s="12">
+        <v>6.6</v>
+      </c>
+      <c r="F28" s="10">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>OH</t>
         </is>
       </c>
-      <c r="E21" s="12">
-        <v>6.5</v>
-      </c>
-      <c r="F21" s="10">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="E22" s="12">
-        <v>6</v>
-      </c>
-      <c r="F22" s="10">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E23" s="12">
-        <v>5.7</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="E29" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="E30" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="F30" s="10">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="E24" s="12">
-        <v>3.9</v>
-      </c>
-      <c r="F24" s="10">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="E25" s="12">
-        <v>3.7</v>
-      </c>
-      <c r="F25" s="10">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="E31" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>All Other (50)</t>
         </is>
       </c>
-      <c r="E26" s="12">
-        <v>52.1</v>
-      </c>
-      <c r="F26" s="10">
-        <v>11691</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="E32" s="12">
+        <v>52.3</v>
+      </c>
+      <c r="F32" s="10">
+        <v>15606</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1019,7 +1142,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">COST_ESTIMATE_REASON
+            <t xml:space="preserve">MECH_ACTIVITY_LOCATION
 </t>
           </r>
           <r>
@@ -1028,155 +1151,514 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Reason the cost estimate was submitted or updated.</t>
+            <t>State or territory whose implementing agency is responsible for the mechanism.</t>
           </r>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>0.6%
-(131)</t>
-        </is>
-      </c>
-      <c r="C27" s="11">
-        <v>13</v>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>A - Inflation Adjusted</t>
-        </is>
-      </c>
-      <c r="E27" s="12">
-        <v>48.4</v>
-      </c>
-      <c r="F27" s="10">
-        <v>10866</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>R - Revised Cost Estimate (Modifications And R...</t>
-        </is>
-      </c>
-      <c r="E28" s="12">
-        <v>22.1</v>
-      </c>
-      <c r="F28" s="10">
-        <v>4969</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>L - Liability Coverage Required</t>
-        </is>
-      </c>
-      <c r="E29" s="12">
-        <v>13.2</v>
-      </c>
-      <c r="F29" s="10">
-        <v>2959</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>I - Initial Cost Estimate</t>
-        </is>
-      </c>
-      <c r="E30" s="12">
-        <v>6.9</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>C - Cost Estimate Not Required Or No Longer Re...</t>
-        </is>
-      </c>
-      <c r="E31" s="12">
-        <v>5.1</v>
-      </c>
-      <c r="F31" s="10">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>All Other (8)</t>
-        </is>
-      </c>
-      <c r="E32" s="12">
-        <v>3.8</v>
-      </c>
-      <c r="F32" s="10">
-        <v>846</v>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>6.6%
+(1961)</t>
+        </is>
+      </c>
+      <c r="C33" s="11">
+        <v>53</v>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="E33" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="F33" s="10">
+        <v>2156</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E34" s="12">
+        <v>7</v>
+      </c>
+      <c r="F34" s="10">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E35" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="F35" s="10">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E36" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="F36" s="10">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E37" s="12">
+        <v>4.7</v>
+      </c>
+      <c r="F37" s="10">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>All Other (48)</t>
+        </is>
+      </c>
+      <c r="E38" s="12">
+        <v>61.5</v>
+      </c>
+      <c r="F38" s="10">
+        <v>18357</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">MECH_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency responsible for the financial mechanism.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>6.6%
+(1961)</t>
+        </is>
+      </c>
+      <c r="C39" s="11">
+        <v>2</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E39" s="12">
+        <v>86.2</v>
+      </c>
+      <c r="F39" s="10">
+        <v>25751</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E40" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="F40" s="10">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">MECH_TYPE_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the mechanism-type code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>6.6%
+(1961)</t>
+        </is>
+      </c>
+      <c r="C41" s="11">
+        <v>4</v>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E41" s="12">
+        <v>92.3</v>
+      </c>
+      <c r="F41" s="10">
+        <v>27552</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E42" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="E43" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="10">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="E44" s="12">
+        <v>0</v>
+      </c>
+      <c r="F44" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">MECH_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of the financial mechanism funding the estimate.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>6.6%
+(1961)</t>
+        </is>
+      </c>
+      <c r="C45" s="11">
+        <v>17</v>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>X - Standby Trust Fund</t>
+        </is>
+      </c>
+      <c r="E45" s="12">
+        <v>20.4</v>
+      </c>
+      <c r="F45" s="10">
+        <v>6083</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>I - Insurance</t>
+        </is>
+      </c>
+      <c r="E46" s="12">
+        <v>17.9</v>
+      </c>
+      <c r="F46" s="10">
+        <v>5354</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>L - Letter Of Credit</t>
+        </is>
+      </c>
+      <c r="E47" s="12">
+        <v>16.7</v>
+      </c>
+      <c r="F47" s="10">
+        <v>4989</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>F - Financial Test</t>
+        </is>
+      </c>
+      <c r="E48" s="12">
+        <v>11</v>
+      </c>
+      <c r="F48" s="10">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>C - Corporate Guarantee</t>
+        </is>
+      </c>
+      <c r="E49" s="12">
+        <v>8.3</v>
+      </c>
+      <c r="F49" s="10">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>All Other (12)</t>
+        </is>
+      </c>
+      <c r="E50" s="12">
+        <v>19.1</v>
+      </c>
+      <c r="F50" s="10">
+        <v>5717</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">ALTERNATIVE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Marks a mechanism accepted as an alternative to the standard instrument.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>95.7%
+(28590)</t>
+        </is>
+      </c>
+      <c r="C51" s="11">
+        <v>2</v>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="F51" s="10">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="10">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
-RESPONSIBLE_PERSON_OWNER: Missing. Incomplete reporting.</t>
-        </is>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+RESPONSIBLE_PERSON_OWNER: Missing. Incomplete reporting.
+MECH_ACTIVITY_LOCATION / MECH_AGENCY / MECH_TYPE_OWNER / MECH_TYPE: Not applicable. Blank on cost estimates with no mechanism on file.
+ALTERNATIVE: Not applicable. Set only on the few mechanisms accepted as an alternative instrument.</t>
+        </is>
+      </c>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Variables dropped (present in the source file but not summarized):
-'COST_COVERAGE_SEQ', 'RESPONSIBLE_PERSON'</t>
-        </is>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+'RESPONSIBLE_PERSON', 'MECH_HANDLER_ID', 'PROVIDER',
+'PROVIDER_CONTACT_NAME', 'PROVIDER_CONTACT_PHONE', 'PROVIDER_CONTACT_EMAIL'</t>
+        </is>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="37">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C3:C4"/>
@@ -1185,20 +1667,35 @@
     <mergeCell ref="A7:A12"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="C7:C12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="A21:A26"/>
     <mergeCell ref="B21:B26"/>
     <mergeCell ref="C21:C26"/>
     <mergeCell ref="A27:A32"/>
     <mergeCell ref="B27:B32"/>
     <mergeCell ref="C27:C32"/>
-    <mergeCell ref="A34:F35"/>
-    <mergeCell ref="A37:F38"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="C33:C38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="B45:B50"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A54:F57"/>
+    <mergeCell ref="A59:F61"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1208,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23"/>
@@ -1259,19 +1756,19 @@
         </is>
       </c>
       <c r="B2" s="10">
-        <v>22101</v>
+        <v>29465</v>
       </c>
       <c r="C2" s="10">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D2" s="21">
         <v>29952</v>
       </c>
       <c r="E2" s="21">
-        <v>39703</v>
+        <v>39745</v>
       </c>
       <c r="F2" s="21">
-        <v>45702</v>
+        <v>45728</v>
       </c>
       <c r="G2" s="21">
         <v>46205</v>
@@ -1284,16 +1781,16 @@
         </is>
       </c>
       <c r="B3" s="10">
-        <v>1479</v>
+        <v>2196</v>
       </c>
       <c r="C3" s="10">
-        <v>93.4</v>
+        <v>92.6</v>
       </c>
       <c r="D3" s="21">
         <v>39903</v>
       </c>
       <c r="E3" s="21">
-        <v>44180</v>
+        <v>44287</v>
       </c>
       <c r="F3" s="21">
         <v>46477</v>
@@ -1305,54 +1802,249 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
+          <t>EFFECTIVE_DATE</t>
+        </is>
+      </c>
+      <c r="B4" s="10">
+        <v>27902</v>
+      </c>
+      <c r="C4" s="10">
+        <v>6.6</v>
+      </c>
+      <c r="D4" s="21">
+        <v>30133</v>
+      </c>
+      <c r="E4" s="21">
+        <v>37966</v>
+      </c>
+      <c r="F4" s="21">
+        <v>45521</v>
+      </c>
+      <c r="G4" s="21">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>EXPIRATION_DATE</t>
+        </is>
+      </c>
+      <c r="B5" s="10">
+        <v>8188</v>
+      </c>
+      <c r="C5" s="10">
+        <v>72.6</v>
+      </c>
+      <c r="D5" s="21">
+        <v>33417</v>
+      </c>
+      <c r="E5" s="21">
+        <v>40268</v>
+      </c>
+      <c r="F5" s="21">
+        <v>46076</v>
+      </c>
+      <c r="G5" s="21">
+        <v>406965</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>COST_COVERAGE_SEQ</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <v>29863</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>36</v>
+      </c>
+      <c r="G6" s="10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>COST_ESTIMATE_AMOUNT</t>
         </is>
       </c>
-      <c r="B4" s="10">
-        <v>22448</v>
-      </c>
-      <c r="C4" s="10">
+      <c r="B7" s="10">
+        <v>29863</v>
+      </c>
+      <c r="C7" s="10">
         <v>0</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E7" s="10">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
-        <v>13180936.6</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="F7" s="10">
+        <v>15000000</v>
+      </c>
+      <c r="G7" s="10">
         <v>444140044</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>MECH_SEQ</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <v>27902</v>
+      </c>
+      <c r="C8" s="10">
+        <v>6.6</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>15</v>
+      </c>
+      <c r="G8" s="10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>MECH_DETAIL_SEQ</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <v>27902</v>
+      </c>
+      <c r="C9" s="10">
+        <v>6.6</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>9</v>
+      </c>
+      <c r="G9" s="10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>FACE_VALUE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <v>27902</v>
+      </c>
+      <c r="C10" s="10">
+        <v>6.6</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>137148590.35</v>
+      </c>
+      <c r="G10" s="10">
+        <v>98157000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>FACILITY_FACE_VALUE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <v>6826</v>
+      </c>
+      <c r="C11" s="10">
+        <v>77.1</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>45473495.75</v>
+      </c>
+      <c r="G11" s="10">
+        <v>88403000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
-UPDATE_DUE_DATE: Not determinable.</t>
-        </is>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+UPDATE_DUE_DATE: Not determinable.
+EFFECTIVE_DATE / EXPIRATION_DATE / MECH_SEQ / MECH_DETAIL_SEQ / FACE_VALUE_AMOUNT / FACILITY_FACE_VALUE_AMOUNT: Not applicable. Blank on cost estimates with no mechanism on file.
+FACILITY_FACE_VALUE_AMOUNT: Also blank where the mechanism covers a single facility, so no facility-level split is recorded.</t>
+        </is>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="A13:G16"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1362,11 +2054,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
-    <col min="2" max="7" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
+    <col min="2" max="9" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1405,6 +2097,16 @@
           <t>No %</t>
         </is>
       </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>Unknown N</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Unknown %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -1419,19 +2121,86 @@
         <v>0</v>
       </c>
       <c r="D2" s="10">
-        <v>4796</v>
+        <v>6156</v>
       </c>
       <c r="E2" s="10">
-        <v>21.36</v>
+        <v>20.61</v>
       </c>
       <c r="F2" s="10">
-        <v>17652</v>
+        <v>23707</v>
       </c>
       <c r="G2" s="10">
-        <v>78.64</v>
-      </c>
+        <v>79.39</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_MECHANISM_DETAIL</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <v>1961</v>
+      </c>
+      <c r="C3" s="10">
+        <v>6.57</v>
+      </c>
+      <c r="D3" s="10">
+        <v>16729</v>
+      </c>
+      <c r="E3" s="10">
+        <v>56.02</v>
+      </c>
+      <c r="F3" s="10">
+        <v>11173</v>
+      </c>
+      <c r="G3" s="10">
+        <v>37.41</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+CURRENT_MECHANISM_DETAIL: Missing. Blank on cost estimates with no mechanism on file.</t>
+        </is>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:I6"/>
+  </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
